--- a/employment_forms/049_employee_reference_form--employment_forms.xlsx
+++ b/employment_forms/049_employee_reference_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,8 +773,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -802,12 +802,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'supervisor'}</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Supervisor'}</t>
+          <t>Supervisor</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'colleague'}</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Colleague'}</t>
+          <t>Colleague</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_0,_'name':_'i_agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 0, 'name': 'I agree'}</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_do_not_agree'}</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I do not agree'}</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
